--- a/output/pdf_financials_xlsx/BTCT.xlsx
+++ b/output/pdf_financials_xlsx/BTCT.xlsx
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>24.078424</v>
       </c>
     </row>
     <row r="93">
@@ -2762,7 +2762,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BTCT.xlsx
+++ b/output/pdf_financials_xlsx/BTCT.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.030017</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +791,7 @@
         <v>-44.21556</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-44.21556</v>
+        <v>-44.245577</v>
       </c>
     </row>
     <row r="28">
@@ -817,7 +817,7 @@
         <v>-44.21556</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-44.21556</v>
+        <v>-44.245577</v>
       </c>
     </row>
     <row r="30">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.740677</v>
       </c>
     </row>
     <row r="35">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.740677</v>
       </c>
     </row>
     <row r="37">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3618,11 +3618,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -3908,7 +3904,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3938,7 +3934,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
